--- a/data/advisor/qiriness-advisor-conversation-notes-v2.xlsx
+++ b/data/advisor/qiriness-advisor-conversation-notes-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnoua\Desktop_backup\APP_DEV\03_Qiriness_Email\Qirines_Email_Automation\data\advisor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E7A89E-A75A-4044-BF86-55E3D6B6F423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A86D67-C869-4706-B928-21E47E397904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5A916513-5A90-4A5C-B959-8503D3CADB3B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Shoujld be able to answer this from the excel sheet that we have, that gives extra product information</t>
+  </si>
+  <si>
+    <t>les crèmes SOS masque Source d'eau best seller et crème non proposées.</t>
+  </si>
+  <si>
+    <t>quand on demande crèmes il propose bien les pots mais pas le SOS tube wrap d'eau</t>
   </si>
 </sst>
 </file>
@@ -206,6 +212,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>8211781</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>77248</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A292F5-3AED-140F-C02D-73B14784877F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14839950"/>
+          <a:ext cx="8821381" cy="7506748"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E37CBF2-0870-410C-BC57-83188B8E822A}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -639,7 +694,18 @@
         <v>22</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>